--- a/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D65B563-282F-428A-B6B5-23FE133D61A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE8EC1EE-E12B-46D0-B3B4-091E19B98F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE8EC1EE-E12B-46D0-B3B4-091E19B98F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BE6A2AE-C376-498B-B16E-3D3A83C1BC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BE6A2AE-C376-498B-B16E-3D3A83C1BC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9198C5BD-BB3A-43C5-9C7F-CBB09F8CB198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9198C5BD-BB3A-43C5-9C7F-CBB09F8CB198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3D8D2A1-9598-4B17-AC57-C3B898F21286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3D8D2A1-9598-4B17-AC57-C3B898F21286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4B6208B-E703-4604-A47F-FB241CBC5BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CAN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4B6208B-E703-4604-A47F-FB241CBC5BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35287B0C-F80E-43CD-883C-318837A87C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="401">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -277,13 +277,25 @@
     <t>CAN</t>
   </si>
   <si>
+    <t>w1108801918-240</t>
+  </si>
+  <si>
+    <t>at grid node - w1108801918-240</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
+  </si>
+  <si>
     <t>w113855788-500</t>
   </si>
   <si>
     <t>at grid node - w113855788-500</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
+    <t>w87373194-315</t>
+  </si>
+  <si>
+    <t>at grid node - w87373194-315</t>
   </si>
   <si>
     <t>w33728777-500</t>
@@ -304,12 +316,24 @@
     <t>at grid node - w117228972-345</t>
   </si>
   <si>
+    <t>w172651669-287</t>
+  </si>
+  <si>
+    <t>at grid node - w172651669-287</t>
+  </si>
+  <si>
     <t>w398222931-240</t>
   </si>
   <si>
     <t>at grid node - w398222931-240</t>
   </si>
   <si>
+    <t>w273447830-240</t>
+  </si>
+  <si>
+    <t>at grid node - w273447830-240</t>
+  </si>
+  <si>
     <t>w398227543-240</t>
   </si>
   <si>
@@ -352,6 +376,12 @@
     <t>at grid node - CA343-765</t>
   </si>
   <si>
+    <t>CA66-240</t>
+  </si>
+  <si>
+    <t>at grid node - CA66-240</t>
+  </si>
+  <si>
     <t>w402099433-240</t>
   </si>
   <si>
@@ -364,12 +394,6 @@
     <t>at grid node - r11490625-240</t>
   </si>
   <si>
-    <t>w273447830-240</t>
-  </si>
-  <si>
-    <t>at grid node - w273447830-240</t>
-  </si>
-  <si>
     <t>w504803035-240</t>
   </si>
   <si>
@@ -394,6 +418,12 @@
     <t>at grid node - w401774037-240</t>
   </si>
   <si>
+    <t>w117955755-345</t>
+  </si>
+  <si>
+    <t>at grid node - w117955755-345</t>
+  </si>
+  <si>
     <t>w334287872-240</t>
   </si>
   <si>
@@ -418,10 +448,10 @@
     <t>at grid node - w1335860683-500</t>
   </si>
   <si>
-    <t>w117955755-345</t>
-  </si>
-  <si>
-    <t>at grid node - w117955755-345</t>
+    <t>w359143129-500</t>
+  </si>
+  <si>
+    <t>at grid node - w359143129-500</t>
   </si>
   <si>
     <t>w33297515-500</t>
@@ -496,6 +526,12 @@
     <t>at grid node - w378545575-240</t>
   </si>
   <si>
+    <t>w269811579-345</t>
+  </si>
+  <si>
+    <t>at grid node - w269811579-345</t>
+  </si>
+  <si>
     <t>w398417877-240</t>
   </si>
   <si>
@@ -550,12 +586,6 @@
     <t>at grid node - CA229-345</t>
   </si>
   <si>
-    <t>w269811579-345</t>
-  </si>
-  <si>
-    <t>at grid node - w269811579-345</t>
-  </si>
-  <si>
     <t>w269999294-345</t>
   </si>
   <si>
@@ -571,6 +601,12 @@
     <t>EN_Hydro_CAN-1,EN_Hydro_CAN-2,EN_Hydro_CAN-3</t>
   </si>
   <si>
+    <t>w398726503-240</t>
+  </si>
+  <si>
+    <t>at grid node - w398726503-240</t>
+  </si>
+  <si>
     <t>w614612290-500</t>
   </si>
   <si>
@@ -643,12 +679,6 @@
     <t>at grid node - r10383760-500</t>
   </si>
   <si>
-    <t>w87373194-315</t>
-  </si>
-  <si>
-    <t>at grid node - w87373194-315</t>
-  </si>
-  <si>
     <t>w323166651-315</t>
   </si>
   <si>
@@ -673,6 +703,12 @@
     <t>at grid node - w322366625-315</t>
   </si>
   <si>
+    <t>w609824151-240</t>
+  </si>
+  <si>
+    <t>at grid node - w609824151-240</t>
+  </si>
+  <si>
     <t>w675398070-240</t>
   </si>
   <si>
@@ -691,18 +727,18 @@
     <t>at grid node - w99457083-500</t>
   </si>
   <si>
+    <t>CA52-315</t>
+  </si>
+  <si>
+    <t>at grid node - CA52-315</t>
+  </si>
+  <si>
     <t>w156738152-500</t>
   </si>
   <si>
     <t>at grid node - w156738152-500</t>
   </si>
   <si>
-    <t>w609824151-240</t>
-  </si>
-  <si>
-    <t>at grid node - w609824151-240</t>
-  </si>
-  <si>
     <t>r12377895-287</t>
   </si>
   <si>
@@ -775,6 +811,12 @@
     <t>at grid node - CA87-315</t>
   </si>
   <si>
+    <t>CA387-500</t>
+  </si>
+  <si>
+    <t>at grid node - CA387-500</t>
+  </si>
+  <si>
     <t>w1001057176-500</t>
   </si>
   <si>
@@ -787,6 +829,12 @@
     <t>at grid node - w1293508819-315</t>
   </si>
   <si>
+    <t>CA376-500</t>
+  </si>
+  <si>
+    <t>at grid node - CA376-500</t>
+  </si>
+  <si>
     <t>CA164-315</t>
   </si>
   <si>
@@ -871,6 +919,12 @@
     <t>at grid node - CA273-315</t>
   </si>
   <si>
+    <t>w268537508-240</t>
+  </si>
+  <si>
+    <t>at grid node - w268537508-240</t>
+  </si>
+  <si>
     <t>CA121-315</t>
   </si>
   <si>
@@ -946,6 +1000,12 @@
     <t>at grid node - w1119149477-240</t>
   </si>
   <si>
+    <t>w832501315-240</t>
+  </si>
+  <si>
+    <t>at grid node - w832501315-240</t>
+  </si>
+  <si>
     <t>CA72-240</t>
   </si>
   <si>
@@ -958,12 +1018,6 @@
     <t>at grid node - w1010206154-240</t>
   </si>
   <si>
-    <t>w832501315-240</t>
-  </si>
-  <si>
-    <t>at grid node - w832501315-240</t>
-  </si>
-  <si>
     <t>CA216-315</t>
   </si>
   <si>
@@ -988,6 +1042,12 @@
     <t>at grid node - w998368251-240</t>
   </si>
   <si>
+    <t>w1112178544-240</t>
+  </si>
+  <si>
+    <t>at grid node - w1112178544-240</t>
+  </si>
+  <si>
     <t>w431214456-240</t>
   </si>
   <si>
@@ -1000,12 +1060,102 @@
     <t>at grid node - w273199686-240</t>
   </si>
   <si>
+    <t>w805809222-315</t>
+  </si>
+  <si>
+    <t>at grid node - w805809222-315</t>
+  </si>
+  <si>
+    <t>CA241-345</t>
+  </si>
+  <si>
+    <t>at grid node - CA241-345</t>
+  </si>
+  <si>
+    <t>w909010599-735</t>
+  </si>
+  <si>
+    <t>at grid node - w909010599-735</t>
+  </si>
+  <si>
+    <t>w80794228-315</t>
+  </si>
+  <si>
+    <t>at grid node - w80794228-315</t>
+  </si>
+  <si>
+    <t>w98752071-315</t>
+  </si>
+  <si>
+    <t>at grid node - w98752071-315</t>
+  </si>
+  <si>
+    <t>w240310383-345</t>
+  </si>
+  <si>
+    <t>at grid node - w240310383-345</t>
+  </si>
+  <si>
+    <t>r13076509-735</t>
+  </si>
+  <si>
+    <t>at grid node - r13076509-735</t>
+  </si>
+  <si>
+    <t>CA58-240</t>
+  </si>
+  <si>
+    <t>at grid node - CA58-240</t>
+  </si>
+  <si>
+    <t>CA139-240</t>
+  </si>
+  <si>
+    <t>at grid node - CA139-240</t>
+  </si>
+  <si>
     <t>w273199064-240</t>
   </si>
   <si>
     <t>at grid node - w273199064-240</t>
   </si>
   <si>
+    <t>w486389136-240</t>
+  </si>
+  <si>
+    <t>at grid node - w486389136-240</t>
+  </si>
+  <si>
+    <t>w486389134-240</t>
+  </si>
+  <si>
+    <t>at grid node - w486389134-240</t>
+  </si>
+  <si>
+    <t>CA83-240</t>
+  </si>
+  <si>
+    <t>at grid node - CA83-240</t>
+  </si>
+  <si>
+    <t>CA92-240</t>
+  </si>
+  <si>
+    <t>at grid node - CA92-240</t>
+  </si>
+  <si>
+    <t>w431696974-240</t>
+  </si>
+  <si>
+    <t>at grid node - w431696974-240</t>
+  </si>
+  <si>
+    <t>w502683515-240</t>
+  </si>
+  <si>
+    <t>at grid node - w502683515-240</t>
+  </si>
+  <si>
     <t>CA112-240</t>
   </si>
   <si>
@@ -1073,12 +1223,6 @@
   </si>
   <si>
     <t>at grid node - w550090303-240</t>
-  </si>
-  <si>
-    <t>w1108801918-240</t>
-  </si>
-  <si>
-    <t>at grid node - w1108801918-240</t>
   </si>
   <si>
     <t>w1132335692-315</t>
@@ -1424,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T131"/>
+  <dimension ref="B3:T156"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:20" x14ac:dyDescent="0.45">
@@ -1529,13 +1673,13 @@
         <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="I11" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="J11" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L11" t="s">
         <v>78</v>
@@ -1547,19 +1691,19 @@
         <v>80</v>
       </c>
       <c r="O11" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q11" t="s">
         <v>78</v>
       </c>
       <c r="R11" t="s">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="S11" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="T11" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -1579,13 +1723,13 @@
         <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="I12" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="J12" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L12" t="s">
         <v>78</v>
@@ -1597,19 +1741,19 @@
         <v>83</v>
       </c>
       <c r="O12" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q12" t="s">
         <v>78</v>
       </c>
       <c r="R12" t="s">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="S12" t="s">
-        <v>328</v>
+        <v>378</v>
       </c>
       <c r="T12" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -1629,13 +1773,13 @@
         <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="I13" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="J13" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L13" t="s">
         <v>78</v>
@@ -1647,19 +1791,19 @@
         <v>85</v>
       </c>
       <c r="O13" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q13" t="s">
         <v>78</v>
       </c>
       <c r="R13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="S13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="T13" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
@@ -1679,13 +1823,13 @@
         <v>78</v>
       </c>
       <c r="H14" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="I14" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="J14" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L14" t="s">
         <v>78</v>
@@ -1697,19 +1841,19 @@
         <v>87</v>
       </c>
       <c r="O14" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q14" t="s">
         <v>78</v>
       </c>
       <c r="R14" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="S14" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="T14" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -1729,37 +1873,37 @@
         <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="I15" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="J15" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L15" t="s">
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>280</v>
+        <v>88</v>
       </c>
       <c r="N15" t="s">
-        <v>281</v>
+        <v>89</v>
       </c>
       <c r="O15" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q15" t="s">
         <v>78</v>
       </c>
       <c r="R15" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="S15" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="T15" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -1779,37 +1923,37 @@
         <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="I16" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="J16" t="s">
+        <v>186</v>
+      </c>
+      <c r="L16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M16" t="s">
+        <v>90</v>
+      </c>
+      <c r="N16" t="s">
+        <v>91</v>
+      </c>
+      <c r="O16" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>78</v>
+      </c>
+      <c r="R16" t="s">
         <v>176</v>
       </c>
-      <c r="L16" t="s">
-        <v>78</v>
-      </c>
-      <c r="M16" t="s">
-        <v>282</v>
-      </c>
-      <c r="N16" t="s">
-        <v>283</v>
-      </c>
-      <c r="O16" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>78</v>
-      </c>
-      <c r="R16" t="s">
-        <v>164</v>
-      </c>
       <c r="S16" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="T16" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
@@ -1829,37 +1973,37 @@
         <v>78</v>
       </c>
       <c r="H17" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="I17" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="J17" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s">
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="N17" t="s">
-        <v>285</v>
+        <v>93</v>
       </c>
       <c r="O17" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q17" t="s">
         <v>78</v>
       </c>
       <c r="R17" t="s">
-        <v>331</v>
+        <v>381</v>
       </c>
       <c r="S17" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="T17" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
@@ -1879,37 +2023,37 @@
         <v>78</v>
       </c>
       <c r="H18" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="I18" t="s">
+        <v>196</v>
+      </c>
+      <c r="J18" t="s">
         <v>186</v>
       </c>
-      <c r="J18" t="s">
-        <v>176</v>
-      </c>
       <c r="L18" t="s">
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="N18" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="O18" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q18" t="s">
         <v>78</v>
       </c>
       <c r="R18" t="s">
-        <v>333</v>
+        <v>383</v>
       </c>
       <c r="S18" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="T18" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
@@ -1929,37 +2073,37 @@
         <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="I19" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="J19" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L19" t="s">
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>170</v>
+        <v>300</v>
       </c>
       <c r="N19" t="s">
-        <v>171</v>
+        <v>301</v>
       </c>
       <c r="O19" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q19" t="s">
         <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="S19" t="s">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="T19" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
@@ -1979,37 +2123,37 @@
         <v>78</v>
       </c>
       <c r="H20" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="I20" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J20" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L20" t="s">
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="N20" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="O20" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q20" t="s">
         <v>78</v>
       </c>
       <c r="R20" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="S20" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="T20" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
@@ -2029,37 +2173,37 @@
         <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="I21" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="J21" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L21" t="s">
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="N21" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="O21" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q21" t="s">
         <v>78</v>
       </c>
       <c r="R21" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="S21" t="s">
-        <v>336</v>
+        <v>386</v>
       </c>
       <c r="T21" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
@@ -2079,37 +2223,37 @@
         <v>78</v>
       </c>
       <c r="H22" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="I22" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="J22" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L22" t="s">
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>292</v>
+        <v>162</v>
       </c>
       <c r="N22" t="s">
-        <v>293</v>
+        <v>163</v>
       </c>
       <c r="O22" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q22" t="s">
         <v>78</v>
       </c>
       <c r="R22" t="s">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="S22" t="s">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="T22" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
@@ -2129,37 +2273,37 @@
         <v>78</v>
       </c>
       <c r="H23" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="I23" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="J23" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L23" t="s">
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>177</v>
+        <v>306</v>
       </c>
       <c r="N23" t="s">
-        <v>178</v>
+        <v>307</v>
       </c>
       <c r="O23" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q23" t="s">
         <v>78</v>
       </c>
       <c r="R23" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="S23" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="T23" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
@@ -2179,37 +2323,37 @@
         <v>78</v>
       </c>
       <c r="H24" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I24" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="J24" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L24" t="s">
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>88</v>
+        <v>308</v>
       </c>
       <c r="N24" t="s">
-        <v>89</v>
+        <v>309</v>
       </c>
       <c r="O24" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q24" t="s">
         <v>78</v>
       </c>
       <c r="R24" t="s">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="S24" t="s">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="T24" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
@@ -2229,37 +2373,37 @@
         <v>78</v>
       </c>
       <c r="H25" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="I25" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="J25" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L25" t="s">
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>90</v>
+        <v>310</v>
       </c>
       <c r="N25" t="s">
-        <v>91</v>
+        <v>311</v>
       </c>
       <c r="O25" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q25" t="s">
         <v>78</v>
       </c>
       <c r="R25" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="S25" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="T25" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
@@ -2279,37 +2423,37 @@
         <v>78</v>
       </c>
       <c r="H26" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I26" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="J26" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L26" t="s">
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="N26" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
       <c r="O26" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q26" t="s">
         <v>78</v>
       </c>
       <c r="R26" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="S26" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="T26" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
@@ -2329,13 +2473,13 @@
         <v>78</v>
       </c>
       <c r="H27" t="s">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L27" t="s">
         <v>78</v>
@@ -2347,19 +2491,19 @@
         <v>95</v>
       </c>
       <c r="O27" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q27" t="s">
         <v>78</v>
       </c>
       <c r="R27" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="S27" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="T27" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
@@ -2379,13 +2523,13 @@
         <v>78</v>
       </c>
       <c r="H28" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="I28" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="J28" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L28" t="s">
         <v>78</v>
@@ -2397,19 +2541,19 @@
         <v>97</v>
       </c>
       <c r="O28" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q28" t="s">
         <v>78</v>
       </c>
       <c r="R28" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="S28" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="T28" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
@@ -2429,13 +2573,13 @@
         <v>78</v>
       </c>
       <c r="H29" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="I29" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="J29" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L29" t="s">
         <v>78</v>
@@ -2447,19 +2591,19 @@
         <v>99</v>
       </c>
       <c r="O29" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q29" t="s">
         <v>78</v>
       </c>
       <c r="R29" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="S29" t="s">
-        <v>342</v>
+        <v>392</v>
       </c>
       <c r="T29" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
@@ -2479,13 +2623,13 @@
         <v>78</v>
       </c>
       <c r="H30" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="I30" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="J30" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s">
         <v>78</v>
@@ -2497,19 +2641,19 @@
         <v>101</v>
       </c>
       <c r="O30" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q30" t="s">
         <v>78</v>
       </c>
       <c r="R30" t="s">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="S30" t="s">
-        <v>344</v>
+        <v>394</v>
       </c>
       <c r="T30" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
@@ -2529,13 +2673,13 @@
         <v>78</v>
       </c>
       <c r="H31" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="J31" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L31" t="s">
         <v>78</v>
@@ -2547,19 +2691,19 @@
         <v>103</v>
       </c>
       <c r="O31" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q31" t="s">
         <v>78</v>
       </c>
       <c r="R31" t="s">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="S31" t="s">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="T31" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
@@ -2579,13 +2723,13 @@
         <v>78</v>
       </c>
       <c r="H32" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="I32" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="J32" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L32" t="s">
         <v>78</v>
@@ -2597,19 +2741,19 @@
         <v>105</v>
       </c>
       <c r="O32" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q32" t="s">
         <v>78</v>
       </c>
       <c r="R32" t="s">
-        <v>347</v>
+        <v>395</v>
       </c>
       <c r="S32" t="s">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="T32" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.45">
@@ -2629,13 +2773,13 @@
         <v>78</v>
       </c>
       <c r="H33" t="s">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
-        <v>214</v>
+        <v>97</v>
       </c>
       <c r="J33" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s">
         <v>78</v>
@@ -2647,19 +2791,19 @@
         <v>107</v>
       </c>
       <c r="O33" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q33" t="s">
         <v>78</v>
       </c>
       <c r="R33" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="S33" t="s">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="T33" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.45">
@@ -2679,13 +2823,13 @@
         <v>78</v>
       </c>
       <c r="H34" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="I34" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="J34" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L34" t="s">
         <v>78</v>
@@ -2697,19 +2841,19 @@
         <v>109</v>
       </c>
       <c r="O34" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q34" t="s">
         <v>78</v>
       </c>
       <c r="R34" t="s">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="S34" t="s">
-        <v>352</v>
+        <v>400</v>
       </c>
       <c r="T34" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.45">
@@ -2729,13 +2873,13 @@
         <v>78</v>
       </c>
       <c r="H35" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="I35" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J35" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L35" t="s">
         <v>78</v>
@@ -2747,19 +2891,19 @@
         <v>111</v>
       </c>
       <c r="O35" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="Q35" t="s">
         <v>78</v>
       </c>
       <c r="R35" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="S35" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="T35" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.45">
@@ -2779,13 +2923,13 @@
         <v>78</v>
       </c>
       <c r="H36" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I36" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="J36" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L36" t="s">
         <v>78</v>
@@ -2797,7 +2941,7 @@
         <v>113</v>
       </c>
       <c r="O36" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
@@ -2817,13 +2961,13 @@
         <v>78</v>
       </c>
       <c r="H37" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="I37" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="J37" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L37" t="s">
         <v>78</v>
@@ -2835,7 +2979,7 @@
         <v>115</v>
       </c>
       <c r="O37" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.45">
@@ -2855,25 +2999,25 @@
         <v>78</v>
       </c>
       <c r="H38" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I38" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="J38" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L38" t="s">
         <v>78</v>
       </c>
       <c r="M38" t="s">
-        <v>294</v>
+        <v>116</v>
       </c>
       <c r="N38" t="s">
-        <v>295</v>
+        <v>117</v>
       </c>
       <c r="O38" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.45">
@@ -2893,25 +3037,25 @@
         <v>78</v>
       </c>
       <c r="H39" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I39" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="J39" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L39" t="s">
         <v>78</v>
       </c>
       <c r="M39" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N39" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O39" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.45">
@@ -2931,25 +3075,25 @@
         <v>78</v>
       </c>
       <c r="H40" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="I40" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="J40" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L40" t="s">
         <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N40" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="O40" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.45">
@@ -2969,25 +3113,25 @@
         <v>78</v>
       </c>
       <c r="H41" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="I41" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="J41" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L41" t="s">
         <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N41" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O41" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.45">
@@ -3007,25 +3151,25 @@
         <v>78</v>
       </c>
       <c r="H42" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="I42" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="J42" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L42" t="s">
         <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>122</v>
+        <v>312</v>
       </c>
       <c r="N42" t="s">
-        <v>123</v>
+        <v>313</v>
       </c>
       <c r="O42" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.45">
@@ -3045,13 +3189,13 @@
         <v>78</v>
       </c>
       <c r="H43" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I43" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="J43" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L43" t="s">
         <v>78</v>
@@ -3063,7 +3207,7 @@
         <v>125</v>
       </c>
       <c r="O43" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.45">
@@ -3083,13 +3227,13 @@
         <v>78</v>
       </c>
       <c r="H44" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="I44" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="J44" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L44" t="s">
         <v>78</v>
@@ -3101,7 +3245,7 @@
         <v>127</v>
       </c>
       <c r="O44" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.45">
@@ -3121,13 +3265,13 @@
         <v>78</v>
       </c>
       <c r="H45" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="I45" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J45" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L45" t="s">
         <v>78</v>
@@ -3139,7 +3283,7 @@
         <v>129</v>
       </c>
       <c r="O45" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.45">
@@ -3159,13 +3303,13 @@
         <v>78</v>
       </c>
       <c r="H46" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I46" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="J46" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L46" t="s">
         <v>78</v>
@@ -3177,7 +3321,7 @@
         <v>131</v>
       </c>
       <c r="O46" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.45">
@@ -3197,13 +3341,13 @@
         <v>78</v>
       </c>
       <c r="H47" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I47" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="J47" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L47" t="s">
         <v>78</v>
@@ -3215,7 +3359,7 @@
         <v>133</v>
       </c>
       <c r="O47" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.45">
@@ -3235,13 +3379,13 @@
         <v>78</v>
       </c>
       <c r="H48" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="I48" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="J48" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L48" t="s">
         <v>78</v>
@@ -3253,7 +3397,7 @@
         <v>135</v>
       </c>
       <c r="O48" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.45">
@@ -3273,13 +3417,13 @@
         <v>78</v>
       </c>
       <c r="H49" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I49" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="J49" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L49" t="s">
         <v>78</v>
@@ -3291,7 +3435,7 @@
         <v>137</v>
       </c>
       <c r="O49" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.45">
@@ -3311,13 +3455,13 @@
         <v>78</v>
       </c>
       <c r="H50" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="I50" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="J50" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L50" t="s">
         <v>78</v>
@@ -3329,7 +3473,7 @@
         <v>139</v>
       </c>
       <c r="O50" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.45">
@@ -3349,13 +3493,13 @@
         <v>78</v>
       </c>
       <c r="H51" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="I51" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="J51" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L51" t="s">
         <v>78</v>
@@ -3367,7 +3511,7 @@
         <v>141</v>
       </c>
       <c r="O51" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.45">
@@ -3387,13 +3531,13 @@
         <v>78</v>
       </c>
       <c r="H52" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="I52" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="J52" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L52" t="s">
         <v>78</v>
@@ -3405,7 +3549,7 @@
         <v>143</v>
       </c>
       <c r="O52" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.45">
@@ -3425,13 +3569,13 @@
         <v>78</v>
       </c>
       <c r="H53" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="I53" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="J53" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L53" t="s">
         <v>78</v>
@@ -3443,7 +3587,7 @@
         <v>145</v>
       </c>
       <c r="O53" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.45">
@@ -3463,13 +3607,13 @@
         <v>78</v>
       </c>
       <c r="H54" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I54" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="J54" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L54" t="s">
         <v>78</v>
@@ -3481,7 +3625,7 @@
         <v>147</v>
       </c>
       <c r="O54" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.45">
@@ -3501,13 +3645,13 @@
         <v>78</v>
       </c>
       <c r="H55" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I55" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="J55" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L55" t="s">
         <v>78</v>
@@ -3519,7 +3663,7 @@
         <v>149</v>
       </c>
       <c r="O55" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.45">
@@ -3539,25 +3683,25 @@
         <v>78</v>
       </c>
       <c r="H56" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I56" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="J56" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L56" t="s">
         <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>296</v>
+        <v>150</v>
       </c>
       <c r="N56" t="s">
-        <v>297</v>
+        <v>151</v>
       </c>
       <c r="O56" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.45">
@@ -3577,143 +3721,203 @@
         <v>78</v>
       </c>
       <c r="H57" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="I57" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="J57" t="s">
+        <v>186</v>
+      </c>
+      <c r="L57" t="s">
+        <v>78</v>
+      </c>
+      <c r="M57" t="s">
+        <v>152</v>
+      </c>
+      <c r="N57" t="s">
+        <v>153</v>
+      </c>
+      <c r="O57" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" t="s">
+        <v>175</v>
+      </c>
+      <c r="E58" t="s">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s">
+        <v>78</v>
+      </c>
+      <c r="H58" t="s">
+        <v>271</v>
+      </c>
+      <c r="I58" t="s">
+        <v>272</v>
+      </c>
+      <c r="J58" t="s">
+        <v>186</v>
+      </c>
+      <c r="L58" t="s">
+        <v>78</v>
+      </c>
+      <c r="M58" t="s">
+        <v>154</v>
+      </c>
+      <c r="N58" t="s">
+        <v>155</v>
+      </c>
+      <c r="O58" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" t="s">
         <v>176</v>
       </c>
-      <c r="L57" t="s">
-        <v>78</v>
-      </c>
-      <c r="M57" t="s">
-        <v>150</v>
-      </c>
-      <c r="N57" t="s">
-        <v>151</v>
-      </c>
-      <c r="O57" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="G58" t="s">
-        <v>78</v>
-      </c>
-      <c r="H58" t="s">
-        <v>102</v>
-      </c>
-      <c r="I58" t="s">
-        <v>103</v>
-      </c>
-      <c r="J58" t="s">
-        <v>176</v>
-      </c>
-      <c r="L58" t="s">
-        <v>78</v>
-      </c>
-      <c r="M58" t="s">
-        <v>152</v>
-      </c>
-      <c r="N58" t="s">
-        <v>153</v>
-      </c>
-      <c r="O58" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="D59" t="s">
+        <v>177</v>
+      </c>
+      <c r="E59" t="s">
+        <v>81</v>
+      </c>
       <c r="G59" t="s">
         <v>78</v>
       </c>
       <c r="H59" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="I59" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="J59" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L59" t="s">
         <v>78</v>
       </c>
       <c r="M59" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N59" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O59" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>78</v>
+      </c>
+      <c r="C60" t="s">
+        <v>178</v>
+      </c>
+      <c r="D60" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" t="s">
+        <v>81</v>
+      </c>
       <c r="G60" t="s">
         <v>78</v>
       </c>
       <c r="H60" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="I60" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="J60" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L60" t="s">
         <v>78</v>
       </c>
       <c r="M60" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N60" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O60" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>78</v>
+      </c>
+      <c r="C61" t="s">
+        <v>180</v>
+      </c>
+      <c r="D61" t="s">
+        <v>181</v>
+      </c>
+      <c r="E61" t="s">
+        <v>81</v>
+      </c>
       <c r="G61" t="s">
         <v>78</v>
       </c>
       <c r="H61" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="I61" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="J61" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L61" t="s">
         <v>78</v>
       </c>
       <c r="M61" t="s">
-        <v>158</v>
+        <v>314</v>
       </c>
       <c r="N61" t="s">
-        <v>159</v>
+        <v>315</v>
       </c>
       <c r="O61" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" t="s">
+        <v>182</v>
+      </c>
+      <c r="D62" t="s">
+        <v>183</v>
+      </c>
+      <c r="E62" t="s">
+        <v>81</v>
+      </c>
       <c r="G62" t="s">
         <v>78</v>
       </c>
       <c r="H62" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="I62" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="J62" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L62" t="s">
         <v>78</v>
@@ -3725,7 +3929,7 @@
         <v>161</v>
       </c>
       <c r="O62" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.45">
@@ -3733,25 +3937,25 @@
         <v>78</v>
       </c>
       <c r="H63" t="s">
-        <v>269</v>
+        <v>110</v>
       </c>
       <c r="I63" t="s">
-        <v>270</v>
+        <v>111</v>
       </c>
       <c r="J63" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L63" t="s">
         <v>78</v>
       </c>
       <c r="M63" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N63" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O63" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.45">
@@ -3759,25 +3963,25 @@
         <v>78</v>
       </c>
       <c r="H64" t="s">
-        <v>271</v>
+        <v>106</v>
       </c>
       <c r="I64" t="s">
-        <v>272</v>
+        <v>107</v>
       </c>
       <c r="J64" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L64" t="s">
         <v>78</v>
       </c>
       <c r="M64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O64" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="7:15" x14ac:dyDescent="0.45">
@@ -3785,25 +3989,25 @@
         <v>78</v>
       </c>
       <c r="H65" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="I65" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="J65" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L65" t="s">
         <v>78</v>
       </c>
       <c r="M65" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N65" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O65" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66" spans="7:15" x14ac:dyDescent="0.45">
@@ -3811,25 +4015,25 @@
         <v>78</v>
       </c>
       <c r="H66" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="I66" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="J66" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L66" t="s">
         <v>78</v>
       </c>
       <c r="M66" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N66" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O66" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67" spans="7:15" x14ac:dyDescent="0.45">
@@ -3837,13 +4041,13 @@
         <v>78</v>
       </c>
       <c r="H67" t="s">
-        <v>164</v>
+        <v>283</v>
       </c>
       <c r="I67" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="J67" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L67" t="s">
         <v>78</v>
@@ -3855,7 +4059,7 @@
         <v>173</v>
       </c>
       <c r="O67" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="7:15" x14ac:dyDescent="0.45">
@@ -3863,25 +4067,25 @@
         <v>78</v>
       </c>
       <c r="H68" t="s">
-        <v>156</v>
+        <v>285</v>
       </c>
       <c r="I68" t="s">
-        <v>157</v>
+        <v>286</v>
       </c>
       <c r="J68" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L68" t="s">
         <v>78</v>
       </c>
       <c r="M68" t="s">
-        <v>298</v>
+        <v>174</v>
       </c>
       <c r="N68" t="s">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="O68" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="7:15" x14ac:dyDescent="0.45">
@@ -3889,109 +4093,181 @@
         <v>78</v>
       </c>
       <c r="H69" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="I69" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="J69" t="s">
+        <v>186</v>
+      </c>
+      <c r="L69" t="s">
+        <v>78</v>
+      </c>
+      <c r="M69" t="s">
         <v>176</v>
       </c>
-      <c r="L69" t="s">
-        <v>78</v>
-      </c>
-      <c r="M69" t="s">
-        <v>300</v>
-      </c>
       <c r="N69" t="s">
-        <v>301</v>
+        <v>177</v>
       </c>
       <c r="O69" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="70" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G70" t="s">
+        <v>78</v>
+      </c>
+      <c r="H70" t="s">
+        <v>289</v>
+      </c>
+      <c r="I70" t="s">
+        <v>290</v>
+      </c>
+      <c r="J70" t="s">
+        <v>186</v>
+      </c>
       <c r="L70" t="s">
         <v>78</v>
       </c>
       <c r="M70" t="s">
-        <v>302</v>
+        <v>178</v>
       </c>
       <c r="N70" t="s">
-        <v>303</v>
+        <v>179</v>
       </c>
       <c r="O70" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G71" t="s">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s">
+        <v>291</v>
+      </c>
+      <c r="I71" t="s">
+        <v>292</v>
+      </c>
+      <c r="J71" t="s">
+        <v>186</v>
+      </c>
       <c r="L71" t="s">
         <v>78</v>
       </c>
       <c r="M71" t="s">
-        <v>304</v>
+        <v>180</v>
       </c>
       <c r="N71" t="s">
-        <v>305</v>
+        <v>181</v>
       </c>
       <c r="O71" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="72" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G72" t="s">
+        <v>78</v>
+      </c>
+      <c r="H72" t="s">
+        <v>176</v>
+      </c>
+      <c r="I72" t="s">
+        <v>177</v>
+      </c>
+      <c r="J72" t="s">
+        <v>186</v>
+      </c>
       <c r="L72" t="s">
         <v>78</v>
       </c>
       <c r="M72" t="s">
-        <v>306</v>
+        <v>182</v>
       </c>
       <c r="N72" t="s">
-        <v>307</v>
+        <v>183</v>
       </c>
       <c r="O72" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="73" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G73" t="s">
+        <v>78</v>
+      </c>
+      <c r="H73" t="s">
+        <v>168</v>
+      </c>
+      <c r="I73" t="s">
+        <v>169</v>
+      </c>
+      <c r="J73" t="s">
+        <v>186</v>
+      </c>
       <c r="L73" t="s">
         <v>78</v>
       </c>
       <c r="M73" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="N73" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="O73" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G74" t="s">
+        <v>78</v>
+      </c>
+      <c r="H74" t="s">
+        <v>293</v>
+      </c>
+      <c r="I74" t="s">
+        <v>294</v>
+      </c>
+      <c r="J74" t="s">
+        <v>186</v>
+      </c>
       <c r="L74" t="s">
         <v>78</v>
       </c>
       <c r="M74" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="N74" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="O74" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G75" t="s">
+        <v>78</v>
+      </c>
+      <c r="H75" t="s">
+        <v>295</v>
+      </c>
+      <c r="I75" t="s">
+        <v>296</v>
+      </c>
+      <c r="J75" t="s">
+        <v>186</v>
+      </c>
       <c r="L75" t="s">
         <v>78</v>
       </c>
       <c r="M75" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="N75" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="O75" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="76" spans="7:15" x14ac:dyDescent="0.45">
@@ -3999,13 +4275,13 @@
         <v>78</v>
       </c>
       <c r="M76" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="N76" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="O76" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="77" spans="7:15" x14ac:dyDescent="0.45">
@@ -4013,13 +4289,13 @@
         <v>78</v>
       </c>
       <c r="M77" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="N77" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="O77" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="78" spans="7:15" x14ac:dyDescent="0.45">
@@ -4027,13 +4303,13 @@
         <v>78</v>
       </c>
       <c r="M78" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="N78" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="O78" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="79" spans="7:15" x14ac:dyDescent="0.45">
@@ -4041,13 +4317,13 @@
         <v>78</v>
       </c>
       <c r="M79" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="N79" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="O79" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="80" spans="7:15" x14ac:dyDescent="0.45">
@@ -4055,13 +4331,13 @@
         <v>78</v>
       </c>
       <c r="M80" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="N80" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="O80" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="81" spans="12:15" x14ac:dyDescent="0.45">
@@ -4069,13 +4345,13 @@
         <v>78</v>
       </c>
       <c r="M81" t="s">
-        <v>174</v>
+        <v>332</v>
       </c>
       <c r="N81" t="s">
-        <v>175</v>
+        <v>333</v>
       </c>
       <c r="O81" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="12:15" x14ac:dyDescent="0.45">
@@ -4083,13 +4359,13 @@
         <v>78</v>
       </c>
       <c r="M82" t="s">
-        <v>179</v>
+        <v>334</v>
       </c>
       <c r="N82" t="s">
-        <v>180</v>
+        <v>335</v>
       </c>
       <c r="O82" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="83" spans="12:15" x14ac:dyDescent="0.45">
@@ -4097,13 +4373,13 @@
         <v>78</v>
       </c>
       <c r="M83" t="s">
-        <v>181</v>
+        <v>336</v>
       </c>
       <c r="N83" t="s">
-        <v>182</v>
+        <v>337</v>
       </c>
       <c r="O83" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="84" spans="12:15" x14ac:dyDescent="0.45">
@@ -4111,13 +4387,13 @@
         <v>78</v>
       </c>
       <c r="M84" t="s">
-        <v>183</v>
+        <v>338</v>
       </c>
       <c r="N84" t="s">
-        <v>184</v>
+        <v>339</v>
       </c>
       <c r="O84" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="85" spans="12:15" x14ac:dyDescent="0.45">
@@ -4125,13 +4401,13 @@
         <v>78</v>
       </c>
       <c r="M85" t="s">
-        <v>185</v>
+        <v>340</v>
       </c>
       <c r="N85" t="s">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="O85" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="12:15" x14ac:dyDescent="0.45">
@@ -4139,13 +4415,13 @@
         <v>78</v>
       </c>
       <c r="M86" t="s">
-        <v>187</v>
+        <v>342</v>
       </c>
       <c r="N86" t="s">
-        <v>188</v>
+        <v>343</v>
       </c>
       <c r="O86" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="87" spans="12:15" x14ac:dyDescent="0.45">
@@ -4153,13 +4429,13 @@
         <v>78</v>
       </c>
       <c r="M87" t="s">
-        <v>189</v>
+        <v>344</v>
       </c>
       <c r="N87" t="s">
-        <v>190</v>
+        <v>345</v>
       </c>
       <c r="O87" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="88" spans="12:15" x14ac:dyDescent="0.45">
@@ -4167,13 +4443,13 @@
         <v>78</v>
       </c>
       <c r="M88" t="s">
-        <v>191</v>
+        <v>346</v>
       </c>
       <c r="N88" t="s">
-        <v>192</v>
+        <v>347</v>
       </c>
       <c r="O88" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="89" spans="12:15" x14ac:dyDescent="0.45">
@@ -4181,13 +4457,13 @@
         <v>78</v>
       </c>
       <c r="M89" t="s">
-        <v>193</v>
+        <v>348</v>
       </c>
       <c r="N89" t="s">
-        <v>194</v>
+        <v>349</v>
       </c>
       <c r="O89" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="90" spans="12:15" x14ac:dyDescent="0.45">
@@ -4195,13 +4471,13 @@
         <v>78</v>
       </c>
       <c r="M90" t="s">
-        <v>195</v>
+        <v>350</v>
       </c>
       <c r="N90" t="s">
-        <v>196</v>
+        <v>351</v>
       </c>
       <c r="O90" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="91" spans="12:15" x14ac:dyDescent="0.45">
@@ -4209,13 +4485,13 @@
         <v>78</v>
       </c>
       <c r="M91" t="s">
-        <v>197</v>
+        <v>352</v>
       </c>
       <c r="N91" t="s">
-        <v>198</v>
+        <v>353</v>
       </c>
       <c r="O91" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="92" spans="12:15" x14ac:dyDescent="0.45">
@@ -4223,13 +4499,13 @@
         <v>78</v>
       </c>
       <c r="M92" t="s">
-        <v>199</v>
+        <v>354</v>
       </c>
       <c r="N92" t="s">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="O92" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="93" spans="12:15" x14ac:dyDescent="0.45">
@@ -4237,13 +4513,13 @@
         <v>78</v>
       </c>
       <c r="M93" t="s">
-        <v>201</v>
+        <v>356</v>
       </c>
       <c r="N93" t="s">
-        <v>202</v>
+        <v>357</v>
       </c>
       <c r="O93" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="94" spans="12:15" x14ac:dyDescent="0.45">
@@ -4251,13 +4527,13 @@
         <v>78</v>
       </c>
       <c r="M94" t="s">
-        <v>203</v>
+        <v>358</v>
       </c>
       <c r="N94" t="s">
-        <v>204</v>
+        <v>359</v>
       </c>
       <c r="O94" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="95" spans="12:15" x14ac:dyDescent="0.45">
@@ -4265,13 +4541,13 @@
         <v>78</v>
       </c>
       <c r="M95" t="s">
-        <v>205</v>
+        <v>360</v>
       </c>
       <c r="N95" t="s">
-        <v>206</v>
+        <v>361</v>
       </c>
       <c r="O95" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="96" spans="12:15" x14ac:dyDescent="0.45">
@@ -4279,13 +4555,13 @@
         <v>78</v>
       </c>
       <c r="M96" t="s">
-        <v>207</v>
+        <v>362</v>
       </c>
       <c r="N96" t="s">
-        <v>208</v>
+        <v>363</v>
       </c>
       <c r="O96" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="97" spans="12:15" x14ac:dyDescent="0.45">
@@ -4293,13 +4569,13 @@
         <v>78</v>
       </c>
       <c r="M97" t="s">
-        <v>209</v>
+        <v>364</v>
       </c>
       <c r="N97" t="s">
-        <v>210</v>
+        <v>365</v>
       </c>
       <c r="O97" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="98" spans="12:15" x14ac:dyDescent="0.45">
@@ -4307,13 +4583,13 @@
         <v>78</v>
       </c>
       <c r="M98" t="s">
-        <v>211</v>
+        <v>366</v>
       </c>
       <c r="N98" t="s">
-        <v>212</v>
+        <v>367</v>
       </c>
       <c r="O98" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="99" spans="12:15" x14ac:dyDescent="0.45">
@@ -4321,13 +4597,13 @@
         <v>78</v>
       </c>
       <c r="M99" t="s">
-        <v>213</v>
+        <v>368</v>
       </c>
       <c r="N99" t="s">
-        <v>214</v>
+        <v>369</v>
       </c>
       <c r="O99" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="100" spans="12:15" x14ac:dyDescent="0.45">
@@ -4335,13 +4611,13 @@
         <v>78</v>
       </c>
       <c r="M100" t="s">
-        <v>215</v>
+        <v>370</v>
       </c>
       <c r="N100" t="s">
-        <v>216</v>
+        <v>371</v>
       </c>
       <c r="O100" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="101" spans="12:15" x14ac:dyDescent="0.45">
@@ -4349,13 +4625,13 @@
         <v>78</v>
       </c>
       <c r="M101" t="s">
-        <v>217</v>
+        <v>372</v>
       </c>
       <c r="N101" t="s">
-        <v>218</v>
+        <v>373</v>
       </c>
       <c r="O101" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="102" spans="12:15" x14ac:dyDescent="0.45">
@@ -4363,13 +4639,13 @@
         <v>78</v>
       </c>
       <c r="M102" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="N102" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="O102" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="103" spans="12:15" x14ac:dyDescent="0.45">
@@ -4377,13 +4653,13 @@
         <v>78</v>
       </c>
       <c r="M103" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="N103" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="O103" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="104" spans="12:15" x14ac:dyDescent="0.45">
@@ -4391,13 +4667,13 @@
         <v>78</v>
       </c>
       <c r="M104" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="N104" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="O104" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="105" spans="12:15" x14ac:dyDescent="0.45">
@@ -4405,13 +4681,13 @@
         <v>78</v>
       </c>
       <c r="M105" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="N105" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="O105" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="106" spans="12:15" x14ac:dyDescent="0.45">
@@ -4419,13 +4695,13 @@
         <v>78</v>
       </c>
       <c r="M106" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="N106" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="O106" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="107" spans="12:15" x14ac:dyDescent="0.45">
@@ -4433,13 +4709,13 @@
         <v>78</v>
       </c>
       <c r="M107" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="N107" t="s">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="O107" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="108" spans="12:15" x14ac:dyDescent="0.45">
@@ -4447,13 +4723,13 @@
         <v>78</v>
       </c>
       <c r="M108" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="N108" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="O108" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="109" spans="12:15" x14ac:dyDescent="0.45">
@@ -4461,13 +4737,13 @@
         <v>78</v>
       </c>
       <c r="M109" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="N109" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="O109" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="110" spans="12:15" x14ac:dyDescent="0.45">
@@ -4475,13 +4751,13 @@
         <v>78</v>
       </c>
       <c r="M110" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="N110" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="O110" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="111" spans="12:15" x14ac:dyDescent="0.45">
@@ -4489,13 +4765,13 @@
         <v>78</v>
       </c>
       <c r="M111" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="N111" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="O111" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="112" spans="12:15" x14ac:dyDescent="0.45">
@@ -4503,13 +4779,13 @@
         <v>78</v>
       </c>
       <c r="M112" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="N112" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="O112" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="113" spans="12:15" x14ac:dyDescent="0.45">
@@ -4517,13 +4793,13 @@
         <v>78</v>
       </c>
       <c r="M113" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="N113" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="O113" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="114" spans="12:15" x14ac:dyDescent="0.45">
@@ -4531,13 +4807,13 @@
         <v>78</v>
       </c>
       <c r="M114" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="N114" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="O114" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="115" spans="12:15" x14ac:dyDescent="0.45">
@@ -4545,13 +4821,13 @@
         <v>78</v>
       </c>
       <c r="M115" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="N115" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="O115" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="116" spans="12:15" x14ac:dyDescent="0.45">
@@ -4559,13 +4835,13 @@
         <v>78</v>
       </c>
       <c r="M116" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="N116" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="O116" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="117" spans="12:15" x14ac:dyDescent="0.45">
@@ -4573,13 +4849,13 @@
         <v>78</v>
       </c>
       <c r="M117" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="N117" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="O117" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="118" spans="12:15" x14ac:dyDescent="0.45">
@@ -4587,13 +4863,13 @@
         <v>78</v>
       </c>
       <c r="M118" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="N118" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="O118" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="119" spans="12:15" x14ac:dyDescent="0.45">
@@ -4601,13 +4877,13 @@
         <v>78</v>
       </c>
       <c r="M119" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="N119" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="O119" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="120" spans="12:15" x14ac:dyDescent="0.45">
@@ -4615,13 +4891,13 @@
         <v>78</v>
       </c>
       <c r="M120" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="N120" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="O120" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="121" spans="12:15" x14ac:dyDescent="0.45">
@@ -4629,13 +4905,13 @@
         <v>78</v>
       </c>
       <c r="M121" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="N121" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="O121" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="122" spans="12:15" x14ac:dyDescent="0.45">
@@ -4643,13 +4919,13 @@
         <v>78</v>
       </c>
       <c r="M122" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="N122" t="s">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="O122" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="123" spans="12:15" x14ac:dyDescent="0.45">
@@ -4657,13 +4933,13 @@
         <v>78</v>
       </c>
       <c r="M123" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="N123" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="O123" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="124" spans="12:15" x14ac:dyDescent="0.45">
@@ -4671,13 +4947,13 @@
         <v>78</v>
       </c>
       <c r="M124" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="N124" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="O124" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="125" spans="12:15" x14ac:dyDescent="0.45">
@@ -4685,13 +4961,13 @@
         <v>78</v>
       </c>
       <c r="M125" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="N125" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="O125" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="126" spans="12:15" x14ac:dyDescent="0.45">
@@ -4699,13 +4975,13 @@
         <v>78</v>
       </c>
       <c r="M126" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="N126" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="O126" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="127" spans="12:15" x14ac:dyDescent="0.45">
@@ -4713,13 +4989,13 @@
         <v>78</v>
       </c>
       <c r="M127" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="N127" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="O127" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="128" spans="12:15" x14ac:dyDescent="0.45">
@@ -4727,13 +5003,13 @@
         <v>78</v>
       </c>
       <c r="M128" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="N128" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="O128" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="129" spans="12:15" x14ac:dyDescent="0.45">
@@ -4741,13 +5017,13 @@
         <v>78</v>
       </c>
       <c r="M129" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="N129" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="O129" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="130" spans="12:15" x14ac:dyDescent="0.45">
@@ -4755,13 +5031,13 @@
         <v>78</v>
       </c>
       <c r="M130" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="N130" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="O130" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="131" spans="12:15" x14ac:dyDescent="0.45">
@@ -4769,13 +5045,363 @@
         <v>78</v>
       </c>
       <c r="M131" t="s">
+        <v>245</v>
+      </c>
+      <c r="N131" t="s">
+        <v>246</v>
+      </c>
+      <c r="O131" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="132" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L132" t="s">
+        <v>78</v>
+      </c>
+      <c r="M132" t="s">
+        <v>247</v>
+      </c>
+      <c r="N132" t="s">
+        <v>248</v>
+      </c>
+      <c r="O132" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="133" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L133" t="s">
+        <v>78</v>
+      </c>
+      <c r="M133" t="s">
+        <v>249</v>
+      </c>
+      <c r="N133" t="s">
+        <v>250</v>
+      </c>
+      <c r="O133" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="134" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L134" t="s">
+        <v>78</v>
+      </c>
+      <c r="M134" t="s">
+        <v>251</v>
+      </c>
+      <c r="N134" t="s">
+        <v>252</v>
+      </c>
+      <c r="O134" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="135" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L135" t="s">
+        <v>78</v>
+      </c>
+      <c r="M135" t="s">
+        <v>253</v>
+      </c>
+      <c r="N135" t="s">
+        <v>254</v>
+      </c>
+      <c r="O135" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="136" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L136" t="s">
+        <v>78</v>
+      </c>
+      <c r="M136" t="s">
+        <v>255</v>
+      </c>
+      <c r="N136" t="s">
+        <v>256</v>
+      </c>
+      <c r="O136" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="137" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L137" t="s">
+        <v>78</v>
+      </c>
+      <c r="M137" t="s">
+        <v>257</v>
+      </c>
+      <c r="N137" t="s">
+        <v>258</v>
+      </c>
+      <c r="O137" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="138" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L138" t="s">
+        <v>78</v>
+      </c>
+      <c r="M138" t="s">
+        <v>259</v>
+      </c>
+      <c r="N138" t="s">
+        <v>260</v>
+      </c>
+      <c r="O138" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="139" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L139" t="s">
+        <v>78</v>
+      </c>
+      <c r="M139" t="s">
+        <v>261</v>
+      </c>
+      <c r="N139" t="s">
+        <v>262</v>
+      </c>
+      <c r="O139" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="140" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L140" t="s">
+        <v>78</v>
+      </c>
+      <c r="M140" t="s">
+        <v>263</v>
+      </c>
+      <c r="N140" t="s">
+        <v>264</v>
+      </c>
+      <c r="O140" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="141" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L141" t="s">
+        <v>78</v>
+      </c>
+      <c r="M141" t="s">
+        <v>265</v>
+      </c>
+      <c r="N141" t="s">
+        <v>266</v>
+      </c>
+      <c r="O141" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="142" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L142" t="s">
+        <v>78</v>
+      </c>
+      <c r="M142" t="s">
+        <v>267</v>
+      </c>
+      <c r="N142" t="s">
+        <v>268</v>
+      </c>
+      <c r="O142" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="143" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L143" t="s">
+        <v>78</v>
+      </c>
+      <c r="M143" t="s">
+        <v>269</v>
+      </c>
+      <c r="N143" t="s">
+        <v>270</v>
+      </c>
+      <c r="O143" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="144" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L144" t="s">
+        <v>78</v>
+      </c>
+      <c r="M144" t="s">
+        <v>271</v>
+      </c>
+      <c r="N144" t="s">
+        <v>272</v>
+      </c>
+      <c r="O144" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="145" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L145" t="s">
+        <v>78</v>
+      </c>
+      <c r="M145" t="s">
+        <v>273</v>
+      </c>
+      <c r="N145" t="s">
+        <v>274</v>
+      </c>
+      <c r="O145" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="146" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L146" t="s">
+        <v>78</v>
+      </c>
+      <c r="M146" t="s">
+        <v>275</v>
+      </c>
+      <c r="N146" t="s">
+        <v>276</v>
+      </c>
+      <c r="O146" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="147" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L147" t="s">
+        <v>78</v>
+      </c>
+      <c r="M147" t="s">
         <v>277</v>
       </c>
-      <c r="N131" t="s">
+      <c r="N147" t="s">
         <v>278</v>
       </c>
-      <c r="O131" t="s">
+      <c r="O147" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="148" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L148" t="s">
+        <v>78</v>
+      </c>
+      <c r="M148" t="s">
         <v>279</v>
+      </c>
+      <c r="N148" t="s">
+        <v>280</v>
+      </c>
+      <c r="O148" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="149" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L149" t="s">
+        <v>78</v>
+      </c>
+      <c r="M149" t="s">
+        <v>281</v>
+      </c>
+      <c r="N149" t="s">
+        <v>282</v>
+      </c>
+      <c r="O149" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="150" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L150" t="s">
+        <v>78</v>
+      </c>
+      <c r="M150" t="s">
+        <v>283</v>
+      </c>
+      <c r="N150" t="s">
+        <v>284</v>
+      </c>
+      <c r="O150" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="151" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L151" t="s">
+        <v>78</v>
+      </c>
+      <c r="M151" t="s">
+        <v>285</v>
+      </c>
+      <c r="N151" t="s">
+        <v>286</v>
+      </c>
+      <c r="O151" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="152" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L152" t="s">
+        <v>78</v>
+      </c>
+      <c r="M152" t="s">
+        <v>287</v>
+      </c>
+      <c r="N152" t="s">
+        <v>288</v>
+      </c>
+      <c r="O152" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="153" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L153" t="s">
+        <v>78</v>
+      </c>
+      <c r="M153" t="s">
+        <v>289</v>
+      </c>
+      <c r="N153" t="s">
+        <v>290</v>
+      </c>
+      <c r="O153" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="154" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L154" t="s">
+        <v>78</v>
+      </c>
+      <c r="M154" t="s">
+        <v>291</v>
+      </c>
+      <c r="N154" t="s">
+        <v>292</v>
+      </c>
+      <c r="O154" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="155" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L155" t="s">
+        <v>78</v>
+      </c>
+      <c r="M155" t="s">
+        <v>293</v>
+      </c>
+      <c r="N155" t="s">
+        <v>294</v>
+      </c>
+      <c r="O155" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="156" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L156" t="s">
+        <v>78</v>
+      </c>
+      <c r="M156" t="s">
+        <v>295</v>
+      </c>
+      <c r="N156" t="s">
+        <v>296</v>
+      </c>
+      <c r="O156" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
